--- a/Ranking.xlsx
+++ b/Ranking.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr codeName="Αυτό_το_βιβλίο_εργασίας" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Το Drive μου\Panhellenic Championship\BV_2026\ΒΑΘΜΟΛΟΓΙΑ 2026\RANKING\package\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Beach Volley\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBDEECC1-6AA2-47F9-BF54-F244B1D90342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B163A357-20F2-4D89-A2A6-6E3B5947941A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CA66308D-B88D-4CA4-9B5A-3E770B1D54C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F226B7BC-48CA-47DF-B0CF-41024FB4A693}"/>
   </bookViews>
   <sheets>
     <sheet name="MEN" sheetId="1" r:id="rId1"/>
@@ -1595,7 +1595,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Βασικό_Αρχική Κατάταξη" xfId="1" xr:uid="{B708FAC7-1707-4EDC-897A-D3047084B78E}"/>
+    <cellStyle name="Βασικό_Αρχική Κατάταξη" xfId="1" xr:uid="{C920BD17-BF7D-47E2-BF72-8730A7BC6903}"/>
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
@@ -2140,7 +2140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC2CD19-D35C-4E40-A0ED-A8286B7A8998}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1CD8F8-020E-436F-BEEE-EF5392F551D8}">
   <sheetPr codeName="Φύλλο7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5067,10 +5067,10 @@
         <v>72</v>
       </c>
       <c r="Q66" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R66" s="14">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="T66" s="9"/>
       <c r="U66" s="16"/>
@@ -5931,10 +5931,10 @@
         <v>72</v>
       </c>
       <c r="Q90" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R90" s="14">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="T90" s="9"/>
       <c r="U90" s="16"/>
@@ -8149,10 +8149,10 @@
       <c r="O158" s="14"/>
       <c r="P158" s="14"/>
       <c r="Q158" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R158" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T158" s="9"/>
       <c r="U158" s="16"/>
@@ -8182,10 +8182,10 @@
       <c r="O159" s="14"/>
       <c r="P159" s="14"/>
       <c r="Q159" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R159" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T159" s="9"/>
       <c r="U159" s="16"/>
@@ -10626,7 +10626,7 @@
         <v>2718</v>
       </c>
       <c r="Q280" s="14">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="R280" s="18">
         <v>119598</v>
@@ -11379,7 +11379,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE27F3A-33ED-4498-89C9-1F8073621AF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079B7FAA-AED3-411C-AB3D-FA5ED872D6C0}">
   <sheetPr codeName="Φύλλο8">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17092,7 +17092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D749B86E-0C17-45DF-B726-6CC7AA834F8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7F86EC-8F11-40AD-9DA0-1591AB46C29A}">
   <sheetPr codeName="Φύλλο9"/>
   <dimension ref="A1:S282"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -19003,7 +19003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3065FD67-57DD-40C0-B8F7-C540E1133332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459B853E-B3BE-4AD3-ABC3-9D7BC2C7D3FB}">
   <sheetPr codeName="Φύλλο10"/>
   <dimension ref="A1:S282"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
